--- a/outputs/monitor_xlsx/20260306.xlsx
+++ b/outputs/monitor_xlsx/20260306.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.005" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2695,7 +2695,7 @@
         <v>-106284</v>
       </c>
       <c r="N23" t="n">
-        <v>18.65</v>
+        <v>12.53</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2753,6 +2753,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>608</v>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H25" t="n">
+        <v>148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>33</v>
+      </c>
+      <c r="K25" t="n">
+        <v>264</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1574</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8924</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260306.xlsx
+++ b/outputs/monitor_xlsx/20260306.xlsx
@@ -544,10 +544,6 @@
           <t>-0.22%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.75%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.11%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-0.39%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+1.60%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+0.89%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-3.93%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+24.17%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+12.21%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-352.36億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-552.22億</t>
@@ -811,7 +774,6 @@
           <t>71.23億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>50.15億</t>
@@ -822,8 +784,6 @@
           <t>250.73億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-288.61億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>12061口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>17715口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-43.79億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>8.17億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>291</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1083</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-628</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-152</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6805</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33611</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22087</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260306.xlsx
+++ b/outputs/monitor_xlsx/20260306.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>76.84999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.71</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>151611</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-75588</v>
       </c>
       <c r="H4" t="n">
-        <v>-449475</v>
+        <v>-525063</v>
       </c>
       <c r="I4" t="n">
         <v>3300</v>
       </c>
       <c r="J4" t="n">
-        <v>10786</v>
+        <v>14086</v>
       </c>
       <c r="K4" t="n">
         <v>44837</v>
@@ -1279,11 +1278,14 @@
         <v>11610</v>
       </c>
       <c r="M4" t="n">
-        <v>39535</v>
+        <v>51145</v>
       </c>
       <c r="N4" t="n">
         <v>-4302619</v>
       </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>926</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-2.63</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>5461</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-979</v>
       </c>
       <c r="H5" t="n">
-        <v>-1539</v>
+        <v>-2518</v>
       </c>
       <c r="I5" t="n">
         <v>-148</v>
       </c>
       <c r="J5" t="n">
-        <v>-46</v>
+        <v>-194</v>
       </c>
       <c r="K5" t="n">
         <v>173</v>
@@ -1334,11 +1336,14 @@
         <v>2940</v>
       </c>
       <c r="M5" t="n">
-        <v>11327</v>
+        <v>14267</v>
       </c>
       <c r="N5" t="n">
         <v>-78809</v>
       </c>
+      <c r="O5" t="n">
+        <v>-4.98</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1320</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-1.12</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>11211</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-777</v>
       </c>
       <c r="H6" t="n">
-        <v>-4481</v>
+        <v>-5258</v>
       </c>
       <c r="I6" t="n">
         <v>144</v>
       </c>
       <c r="J6" t="n">
-        <v>1073</v>
+        <v>1217</v>
       </c>
       <c r="K6" t="n">
         <v>149</v>
@@ -1389,11 +1394,14 @@
         <v>5736</v>
       </c>
       <c r="M6" t="n">
-        <v>23657</v>
+        <v>29393</v>
       </c>
       <c r="N6" t="n">
         <v>-648960</v>
       </c>
+      <c r="O6" t="n">
+        <v>3.45</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1890</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-0.53</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>34307</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-10927</v>
       </c>
       <c r="H7" t="n">
-        <v>-77844</v>
+        <v>-88771</v>
       </c>
       <c r="I7" t="n">
         <v>946</v>
       </c>
       <c r="J7" t="n">
-        <v>6863</v>
+        <v>7809</v>
       </c>
       <c r="K7" t="n">
         <v>342</v>
@@ -1444,11 +1452,14 @@
         <v>23632</v>
       </c>
       <c r="M7" t="n">
-        <v>90116</v>
+        <v>113748</v>
       </c>
       <c r="N7" t="n">
         <v>-6482976</v>
       </c>
+      <c r="O7" t="n">
+        <v>1.22</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1465</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>3.17</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>6338</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="I8" t="n">
         <v>434</v>
       </c>
       <c r="J8" t="n">
-        <v>-256</v>
+        <v>178</v>
       </c>
       <c r="K8" t="n">
         <v>68</v>
@@ -1499,11 +1510,14 @@
         <v>1767</v>
       </c>
       <c r="M8" t="n">
-        <v>7557</v>
+        <v>9324</v>
       </c>
       <c r="N8" t="n">
         <v>-140155</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.24</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1375</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-2.14</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>1579</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-161</v>
       </c>
       <c r="H9" t="n">
-        <v>-2001</v>
+        <v>-2162</v>
       </c>
       <c r="I9" t="n">
         <v>38</v>
       </c>
       <c r="J9" t="n">
-        <v>886</v>
+        <v>924</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -1554,11 +1568,14 @@
         <v>3199</v>
       </c>
       <c r="M9" t="n">
-        <v>10157</v>
+        <v>13356</v>
       </c>
       <c r="N9" t="n">
         <v>-106284</v>
       </c>
+      <c r="O9" t="n">
+        <v>18.65</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2360</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-0.21</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2912</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-463</v>
       </c>
       <c r="H10" t="n">
-        <v>-742</v>
+        <v>-1205</v>
       </c>
       <c r="I10" t="n">
         <v>172</v>
       </c>
       <c r="J10" t="n">
-        <v>848</v>
+        <v>1019</v>
       </c>
       <c r="K10" t="n">
         <v>22</v>
@@ -1609,11 +1626,14 @@
         <v>1896</v>
       </c>
       <c r="M10" t="n">
-        <v>7375</v>
+        <v>9271</v>
       </c>
       <c r="N10" t="n">
         <v>-89498</v>
       </c>
+      <c r="O10" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1895</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-4.53</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>5169</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>410</v>
       </c>
       <c r="H11" t="n">
-        <v>-797</v>
+        <v>-388</v>
       </c>
       <c r="I11" t="n">
         <v>-4</v>
       </c>
       <c r="J11" t="n">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -1664,11 +1684,14 @@
         <v>4723</v>
       </c>
       <c r="M11" t="n">
-        <v>17757</v>
+        <v>22480</v>
       </c>
       <c r="N11" t="n">
         <v>-19139</v>
       </c>
+      <c r="O11" t="n">
+        <v>-1.99</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>5250</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>608</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>-81</v>
+        <v>-41</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
       </c>
       <c r="J12" t="n">
-        <v>-103</v>
+        <v>45</v>
       </c>
       <c r="K12" t="n">
         <v>33</v>
@@ -1719,11 +1742,14 @@
         <v>264</v>
       </c>
       <c r="M12" t="n">
-        <v>1310</v>
+        <v>1574</v>
       </c>
       <c r="N12" t="n">
         <v>-8924</v>
       </c>
+      <c r="O12" t="n">
+        <v>14.03</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-233</v>
       </c>
       <c r="H13" t="n">
-        <v>-1072</v>
+        <v>-1305</v>
       </c>
       <c r="I13" t="n">
         <v>440</v>
       </c>
       <c r="J13" t="n">
-        <v>1004</v>
+        <v>1444</v>
       </c>
       <c r="K13" t="n">
         <v>143</v>
@@ -1774,11 +1800,14 @@
         <v>-106</v>
       </c>
       <c r="M13" t="n">
-        <v>47</v>
+        <v>-59</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,20 +1830,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-112</v>
       </c>
       <c r="H14" t="n">
-        <v>1683</v>
+        <v>1571</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-985</v>
@@ -1826,11 +1858,14 @@
         <v>181</v>
       </c>
       <c r="M14" t="n">
-        <v>-956</v>
+        <v>-775</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>-122</v>
       </c>
       <c r="H15" t="n">
-        <v>2737</v>
+        <v>2615</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>330</v>
@@ -1878,11 +1916,14 @@
         <v>-116</v>
       </c>
       <c r="M15" t="n">
-        <v>-118</v>
+        <v>-234</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1905,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>190</v>
       </c>
       <c r="H16" t="n">
-        <v>237</v>
+        <v>427</v>
       </c>
       <c r="I16" t="n">
         <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
         <v>50</v>
@@ -1933,11 +1974,14 @@
         <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>-96</v>
+        <v>-15</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>291</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>5.43</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1083</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-53</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-628</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-4</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-152</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6805</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>33611</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22087</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.91</v>
+      <c r="O17" t="n">
+        <v>13.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260306.xlsx
+++ b/outputs/monitor_xlsx/20260306.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>13.58</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4669</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-955</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9979</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-65</v>
+      </c>
+      <c r="J18" t="n">
+        <v>447</v>
+      </c>
+      <c r="K18" t="n">
+        <v>147</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5873</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29129</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400920</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>432</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13951</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-4620</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-7322</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-124</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-576</v>
+      </c>
+      <c r="K19" t="n">
+        <v>251</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40081</v>
+      </c>
+      <c r="M19" t="n">
+        <v>204668</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392121</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2398</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>858</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3204</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>595</v>
+      </c>
+      <c r="K20" t="n">
+        <v>295</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9816</v>
+      </c>
+      <c r="M20" t="n">
+        <v>54780</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161490</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-3.06</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
